--- a/FASE 2/Cálculo de Aderência.xlsx
+++ b/FASE 2/Cálculo de Aderência.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pucpredu-my.sharepoint.com/personal/stefany_oliveira_pucpr_edu_br/Documents/Documentos/GitHub/PROJETO-EXPERIENCIA-CRIATIVA-INOVANDO-EM-PROCESSOS/FASE 1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pucpredu-my.sharepoint.com/personal/stefany_oliveira_pucpr_edu_br/Documents/Documentos/GitHub/PROJETO-EXPERIENCIA-CRIATIVA-INOVANDO-EM-PROCESSOS/FASE 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{E5F1155B-384C-451C-871D-3630B7CFA6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9921809E-9D67-41BA-9B8A-AFBD9091E91A}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{E5F1155B-384C-451C-871D-3630B7CFA6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4ABF1FF-A08F-4D43-9036-3CF2C0BE6BBD}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{2BA9A6CF-492F-4CCB-A27F-FFC55E200CD8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2BA9A6CF-492F-4CCB-A27F-FFC55E200CD8}"/>
   </bookViews>
   <sheets>
     <sheet name="Planejamento da Entrevista" sheetId="1" r:id="rId1"/>
@@ -1564,10 +1564,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>39</c:v>
+                  <c:v>47</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2592,10 +2592,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3309,10 +3309,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11681,10 +11681,6 @@
 </FeaturePropertyBags>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
@@ -12624,7 +12620,7 @@
         <v>61</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -12635,7 +12631,7 @@
         <v>62</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -12646,7 +12642,7 @@
         <v>63</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -12657,7 +12653,7 @@
         <v>64</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -12681,15 +12677,15 @@
       </c>
       <c r="B61" s="3">
         <f>COUNTIFS($C$56:$C$60, "Atende*")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C61" s="3">
         <f>COUNTIFS($C$56:$C$60, "Não atende*")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D61" s="9">
         <f>(B61/A61)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -12926,7 +12922,7 @@
         <v>88</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -12937,7 +12933,7 @@
         <v>89</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -12959,7 +12955,7 @@
         <v>91</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -12970,7 +12966,7 @@
         <v>92</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -12994,15 +12990,15 @@
       </c>
       <c r="B90" s="3">
         <f>COUNTIFS($C$84:$C$88, "Atende*")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C90" s="3">
         <f>COUNTIFS($C$84:$C$88, "Não atende*")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D90" s="9">
         <f>(B90/A90)</f>
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -13451,15 +13447,15 @@
       </c>
       <c r="B134" s="3">
         <f>COUNTIFS($C$3:$C$126, "Atende*")</f>
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C134" s="3">
         <f>COUNTIFS($C$3:$C$126, "Não atende*")</f>
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D134" s="6">
         <f>(B134/A134)</f>
-        <v>0.56521739130434778</v>
+        <v>0.6811594202898551</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
@@ -13585,11 +13581,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d4c4f424-04dc-4067-abf7-2cdaf5be40b7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13826,27 +13823,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d4c4f424-04dc-4067-abf7-2cdaf5be40b7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{924656E7-7DAC-4850-9A06-F6B76FD8F491}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF95609E-6CCE-44D6-BD6A-38C9BFA1C94E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="59a2b59b-6ce1-4938-bf5c-70297f05899c"/>
-    <ds:schemaRef ds:uri="d4c4f424-04dc-4067-abf7-2cdaf5be40b7"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13871,9 +13858,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF95609E-6CCE-44D6-BD6A-38C9BFA1C94E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{924656E7-7DAC-4850-9A06-F6B76FD8F491}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="59a2b59b-6ce1-4938-bf5c-70297f05899c"/>
+    <ds:schemaRef ds:uri="d4c4f424-04dc-4067-abf7-2cdaf5be40b7"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
